--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6219-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6219-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F71687FD-540D-4F2F-9A21-2FD34ADFB7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDB2639F-D1EC-4628-AC86-F3DE9ED2C870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{D7306C71-22B8-4047-B162-59133FE4723D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{484FAB22-895B-43CF-AC54-EB9849509DC7}"/>
   </bookViews>
   <sheets>
     <sheet name="6219-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1541,30 +1541,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A97459F-EBC1-45D7-9903-E38B8FDC6A1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{658A2E35-630E-4A64-92AA-30D09E065261}">
   <dimension ref="A1:X65"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1598,7 +1598,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1634,7 +1634,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1754,7 +1754,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="41">
         <v>2024</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="43"/>
       <c r="B10" s="44"/>
       <c r="C10" s="18" t="s">
@@ -2148,7 +2148,7 @@
       <c r="W10" s="50"/>
       <c r="X10" s="46"/>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
         <v>29</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="48"/>
       <c r="B12" s="48"/>
       <c r="C12" s="20" t="s">
@@ -2250,7 +2250,7 @@
       <c r="W12" s="50"/>
       <c r="X12" s="46"/>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2023</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="53">
         <v>2022</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>29</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2021</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>29</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>29</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>29</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>29</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <v>2020</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>29</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="16" t="s">
         <v>29</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
         <v>29</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
         <v>29</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>29</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>2019</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>9.65</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>29</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
         <v>29</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
         <v>29</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="53">
         <v>2018</v>
       </c>
@@ -4754,7 +4754,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>2017</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="53">
         <v>2016</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>2015</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="53">
         <v>2014</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39">
         <v>2013</v>
       </c>
@@ -5114,7 +5114,7 @@
         <v>9.65</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <v>2012</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="39">
         <v>2011</v>
       </c>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="53">
         <v>2010</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="39">
         <v>2009</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="53">
         <v>2008</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="39">
         <v>2007</v>
       </c>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="53">
         <v>2006</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="39">
         <v>2005</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="53">
         <v>2004</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="39">
         <v>2003</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="53">
         <v>2002</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="39">
         <v>2001</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="53">
         <v>2000</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="39" t="s">
         <v>52</v>
       </c>
